--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/phi-4/metrics_default_vs_simple.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/phi-4/metrics_default_vs_simple.xlsx
@@ -420,16 +420,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.3583333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C2">
-        <v>0.3732394366197183</v>
+        <v>0.4154929577464789</v>
       </c>
       <c r="D2">
-        <v>0.6742424242424242</v>
+        <v>0.6287878787878788</v>
       </c>
       <c r="E2">
         <v>120</v>
